--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/ARIZONA_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/ARIZONA_2010.xlsx
@@ -2634,7 +2634,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C127">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C261">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C765">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C821">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C865">
@@ -21426,7 +21426,7 @@
       </c>
       <c r="B1171" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1171">
@@ -21534,7 +21534,7 @@
       </c>
       <c r="B1177" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1177">
@@ -22740,7 +22740,7 @@
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1244">
